--- a/datos/ejemplos_empresas.xlsx
+++ b/datos/ejemplos_empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{E3968524-56AA-4ED7-8BA0-7E46E3840944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D17A225-F689-4E2C-96A4-F2A580F85158}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{E3968524-56AA-4ED7-8BA0-7E46E3840944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FFFACFB-8729-4B10-9FFB-F566472DF2F0}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="23595" windowHeight="14250" xr2:uid="{36A48B76-50FA-4C2B-B697-2A79038C0BE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{36A48B76-50FA-4C2B-B697-2A79038C0BE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
   <si>
     <t>litros/kg</t>
   </si>
@@ -57,16 +57,101 @@
   </si>
   <si>
     <t>queso expedición</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>euros</t>
+  </si>
+  <si>
+    <t>euros/kg</t>
+  </si>
+  <si>
+    <t>Materia grasa</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>Proteína</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Precio
+total
+(euros)</t>
+  </si>
+  <si>
+    <t>Precio unitario
+(euros/kg)</t>
+  </si>
+  <si>
+    <t>Análisis de la 
+leche comprada</t>
+  </si>
+  <si>
+    <t>Análisis del
+queso vendido</t>
+  </si>
+  <si>
+    <t>Extracto seco total (EST)</t>
+  </si>
+  <si>
+    <t>Materia grasa (MG)</t>
+  </si>
+  <si>
+    <t>Extracto seco magro (ESM)</t>
+  </si>
+  <si>
+    <t>Balance de materia</t>
+  </si>
+  <si>
+    <t>MP/ESP</t>
+  </si>
+  <si>
+    <t>Balance total</t>
+  </si>
+  <si>
+    <t>% recuperacion materia</t>
+  </si>
+  <si>
+    <t>Comprado
+(kg)</t>
+  </si>
+  <si>
+    <t>Vendido
+(kg)</t>
+  </si>
+  <si>
+    <t>Pérdidas
+(kg)</t>
+  </si>
+  <si>
+    <t>Coste de la pérdida
+(euros)</t>
+  </si>
+  <si>
+    <t>Facturación</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,16 +159,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -91,18 +197,245 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -117,6 +450,259 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9181F950-CBB9-75FD-AA66-25033939BF44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7248525" y="2819400"/>
+          <a:ext cx="3419475" cy="1152525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51E86D03-8C46-3E63-AF04-250BB74CB618}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7239000" y="4381500"/>
+          <a:ext cx="3857625" cy="1343025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92006B3F-381D-A9B7-03D3-6612E676E9D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7239000" y="6096000"/>
+          <a:ext cx="5514975" cy="1152525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9423A5-311E-7097-19E8-BBEDD927CDCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7239000" y="7810500"/>
+          <a:ext cx="5514975" cy="1152525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -436,24 +1022,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8FF03B8-E965-4443-8C16-957ED6FE43C6}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="3">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="3">
-        <v>1200000</v>
+        <v>1300000</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
@@ -482,21 +1073,21 @@
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>A1*(1-A2)</f>
-        <v>1164000</v>
+        <v>1261000</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="D3" s="3">
         <f>D1*(1-D2)</f>
-        <v>1116000</v>
+        <v>1209000</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="3">
         <f>G1*(1-G2)</f>
-        <v>1182000</v>
+        <v>1280500</v>
       </c>
       <c r="H3" t="s">
         <v>4</v>
@@ -525,29 +1116,29 @@
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f>A3/A4</f>
-        <v>145500</v>
+        <v>157625</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1">
         <f>D3/D4</f>
-        <v>159428.57142857142</v>
+        <v>172714.28571428571</v>
       </c>
       <c r="E5" t="s">
         <v>1</v>
       </c>
       <c r="G5" s="1">
         <f>G3/G4</f>
-        <v>147750</v>
+        <v>160062.5</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>0.17</v>
+      <c r="A6" s="4">
+        <v>0.17519999999999999</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -568,27 +1159,413 @@
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f>A5*(1-A6)</f>
-        <v>120765</v>
+        <v>130009.09999999999</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="3">
         <f>D5*(1-D6)</f>
-        <v>140297.14285714284</v>
+        <v>151988.57142857142</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="3">
         <f>G5*(1-G6)</f>
-        <v>122632.5</v>
+        <v>132851.875</v>
       </c>
       <c r="H7" t="s">
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="34">
+        <f>B15*A7</f>
+        <v>1560109.2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="17">
+        <f>A1*A12</f>
+        <v>53300</v>
+      </c>
+      <c r="C19" s="18">
+        <v>5.5467190048837516</v>
+      </c>
+      <c r="D19" s="17">
+        <f>C19*B19</f>
+        <v>295640.12296030397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="17">
+        <f>A1*A13</f>
+        <v>44850.000000000007</v>
+      </c>
+      <c r="C20" s="18">
+        <v>9.8876295304449471</v>
+      </c>
+      <c r="D20" s="17">
+        <f>C20*B20</f>
+        <v>443460.18444045592</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="22">
+        <f>SUM(D19:D20)</f>
+        <v>739100.30740075989</v>
+      </c>
+      <c r="E21" s="3">
+        <f>B16-D21</f>
+        <v>821008.89259924006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="17">
+        <f>A9*A7</f>
+        <v>71505.005000000005</v>
+      </c>
+      <c r="D25" s="24"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="17">
+        <f>A10*A7</f>
+        <v>36402.548000000003</v>
+      </c>
+      <c r="C26" s="18">
+        <v>5.5467190048837516</v>
+      </c>
+      <c r="D26" s="17">
+        <f>C26*B26</f>
+        <v>201914.70481779301</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="17">
+        <v>35102</v>
+      </c>
+      <c r="C27" s="18">
+        <v>9.8876295304449471</v>
+      </c>
+      <c r="D27" s="17">
+        <f>C27*B27</f>
+        <v>347075.57177767856</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="22">
+        <f>SUM(D26:D27)</f>
+        <v>548990.27659547154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" s="5"/>
+    </row>
+    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="33">
+        <f>B19</f>
+        <v>53300</v>
+      </c>
+      <c r="C32" s="33">
+        <f>B26</f>
+        <v>36402.548000000003</v>
+      </c>
+      <c r="D32" s="27">
+        <f>C32-B32</f>
+        <v>-16897.451999999997</v>
+      </c>
+      <c r="E32" s="33">
+        <f>D32*C26</f>
+        <v>-93725.418142510942</v>
+      </c>
+      <c r="F32" s="28">
+        <f>C32/B32</f>
+        <v>0.68297463414634152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="10">
+        <f>B20</f>
+        <v>44850.000000000007</v>
+      </c>
+      <c r="C33" s="10">
+        <f>B27</f>
+        <v>35102</v>
+      </c>
+      <c r="D33" s="7">
+        <f>C33-B33</f>
+        <v>-9748.0000000000073</v>
+      </c>
+      <c r="E33" s="10">
+        <f>D33*C27</f>
+        <v>-96384.612662777421</v>
+      </c>
+      <c r="F33" s="29">
+        <f>C33/B33</f>
+        <v>0.78265328874024509</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="12">
+        <f>SUM(E32:E33)</f>
+        <v>-190110.03080528835</v>
+      </c>
+      <c r="F34" s="31"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E35" s="5">
+        <f>E34/B16</f>
+        <v>-0.12185687438115765</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="33">
+        <f>B32</f>
+        <v>53300</v>
+      </c>
+      <c r="C37" s="35">
+        <f>B37*F37</f>
+        <v>47970</v>
+      </c>
+      <c r="D37" s="33">
+        <f>C37-B37</f>
+        <v>-5330</v>
+      </c>
+      <c r="E37" s="33">
+        <f>D37*C26</f>
+        <v>-29564.012296030396</v>
+      </c>
+      <c r="F37" s="36">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" s="10">
+        <f>B33</f>
+        <v>44850.000000000007</v>
+      </c>
+      <c r="C38" s="37">
+        <f>B38*F38</f>
+        <v>40365.000000000007</v>
+      </c>
+      <c r="D38" s="10">
+        <f>C38-B38</f>
+        <v>-4485</v>
+      </c>
+      <c r="E38" s="10">
+        <f>D38*C27</f>
+        <v>-44346.018444045585</v>
+      </c>
+      <c r="F38" s="38">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="12">
+        <f>SUM(E37:E38)</f>
+        <v>-73910.030740075978</v>
+      </c>
+      <c r="F39" s="31"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E40" s="23">
+        <f>E39/B16</f>
+        <v>-4.7374908589780752E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E41" s="3">
+        <f>E34-E39</f>
+        <v>-116200.00006521237</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="23">
+        <f>(E34-E39)/E34</f>
+        <v>0.61122498151728244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E43" s="23">
+        <f>E39/E34</f>
+        <v>0.38877501848271756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/datos/ejemplos_empresas.xlsx
+++ b/datos/ejemplos_empresas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\OneDrive\Documentos\GitHub\master-queseria\website\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{E3968524-56AA-4ED7-8BA0-7E46E3840944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FFFACFB-8729-4B10-9FFB-F566472DF2F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11055F31-17DA-4C5B-9F6F-EDDA202C5C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{36A48B76-50FA-4C2B-B697-2A79038C0BE9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="34">
   <si>
     <t>litros/kg</t>
   </si>
@@ -63,15 +63,6 @@
   </si>
   <si>
     <t>MG</t>
-  </si>
-  <si>
-    <t>MP</t>
-  </si>
-  <si>
-    <t>euros</t>
-  </si>
-  <si>
-    <t>euros/kg</t>
   </si>
   <si>
     <t>Materia grasa</t>
@@ -140,7 +131,22 @@
 (euros)</t>
   </si>
   <si>
-    <t>Facturación</t>
+    <t>salida sal</t>
+  </si>
+  <si>
+    <t>leche</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>expedicion y venta</t>
+  </si>
+  <si>
+    <t>ESM</t>
+  </si>
+  <si>
+    <t>HFD</t>
   </si>
 </sst>
 </file>
@@ -149,7 +155,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -371,7 +377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -379,7 +385,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -400,7 +405,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -413,7 +418,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -426,10 +431,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -458,13 +460,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -519,21 +521,21 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Imagen 6">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51E86D03-8C46-3E63-AF04-250BB74CB618}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{428D3475-0F8E-88A6-B363-5226710CDA75}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -556,69 +558,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7239000" y="4381500"/>
+          <a:off x="7239000" y="5715000"/>
           <a:ext cx="3857625" cy="1343025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Imagen 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92006B3F-381D-A9B7-03D3-6612E676E9D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="7239000" y="6096000"/>
-          <a:ext cx="5514975" cy="1152525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -652,10 +593,71 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Imagen 8">
+        <xdr:cNvPr id="10" name="Imagen 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB9423A5-311E-7097-19E8-BBEDD927CDCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4F07208-F4E6-CA31-F431-865EB0B467A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7239000" y="7429500"/>
+          <a:ext cx="5514975" cy="1152525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55FDD15-DC39-1DD1-F81F-3BCEB613DB3E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -678,7 +680,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7239000" y="7810500"/>
+          <a:off x="7239000" y="8763000"/>
           <a:ext cx="5514975" cy="1152525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -699,10 +701,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1022,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8FF03B8-E965-4443-8C16-957ED6FE43C6}">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
@@ -1179,389 +1177,593 @@
         <v>6</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>0.55000000000000004</v>
+        <v>0.52</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
+      <c r="D9" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>0.28000000000000003</v>
+        <v>0.27</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
+      <c r="D10" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <f>A9-A10</f>
+        <v>0.25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <f>D9-D10</f>
+        <v>0.25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="2">
+        <f>G9-G10</f>
+        <v>0.25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>4.1000000000000002E-2</v>
+      <c r="A12" s="2">
+        <f>(1-A9)/(1-A10)</f>
+        <v>0.65753424657534243</v>
       </c>
       <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <f>(1-D9)/(1-D10)</f>
+        <v>0.65753424657534243</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2">
+        <f>(1-G9)/(1-G10)</f>
+        <v>0.65753424657534243</v>
+      </c>
+      <c r="H12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <f>A9/(1-A6)</f>
+        <v>0.63045586808923382</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="2">
+        <f>D9/(1-D6)</f>
+        <v>0.59090909090909094</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2">
+        <f>G9/(1-G6)</f>
+        <v>0.62650602409638556</v>
+      </c>
+      <c r="H14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <f>A10/(1-A6)</f>
+        <v>0.32735208535402527</v>
+      </c>
+      <c r="B15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>3.4500000000000003E-2</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C15" s="4"/>
+      <c r="D15" s="2">
+        <f>D10/(1-D6)</f>
+        <v>0.30681818181818182</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2">
+        <f>G10/(1-G6)</f>
+        <v>0.32530120481927716</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <f>A14-A15</f>
+        <v>0.30310378273520855</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2">
+        <f>D14-D15</f>
+        <v>0.28409090909090912</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="2">
+        <f>G14-G15</f>
+        <v>0.3012048192771084</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <f>(1-A14)/(1-A15)</f>
+        <v>0.54938716654650321</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2">
+        <f>(1-D14)/(1-D15)</f>
+        <v>0.5901639344262295</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="2">
+        <f>(1-G14)/(1-G15)</f>
+        <v>0.5535714285714286</v>
+      </c>
+      <c r="H17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>3.45</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <v>3.45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20">
+        <v>3.45</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15">
+      <c r="B24" s="16">
+        <f>A1*A19/100</f>
+        <v>53300</v>
+      </c>
+      <c r="C24" s="17">
+        <v>5.5467190048837516</v>
+      </c>
+      <c r="D24" s="16">
+        <f>C24*B24</f>
+        <v>295640.12296030397</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="16">
+        <f>A1*A20/100</f>
+        <v>44850</v>
+      </c>
+      <c r="C25" s="17">
+        <v>9.8876295304449471</v>
+      </c>
+      <c r="D25" s="16">
+        <f>C25*B25</f>
+        <v>443460.18444045587</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="34">
-        <f>B15*A7</f>
-        <v>1560109.2</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="21">
+        <f>SUM(D24:D25)</f>
+        <v>739100.30740075978</v>
+      </c>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+      <c r="C29" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="16">
+        <f>A14*A7</f>
+        <v>81965</v>
+      </c>
+      <c r="D30" s="23"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="B31" s="16">
+        <f>A15*A7</f>
+        <v>42558.750000000007</v>
+      </c>
+      <c r="C31" s="17">
+        <v>5.5467190048837516</v>
+      </c>
+      <c r="D31" s="16">
+        <f>C31*B31</f>
+        <v>236061.4274490964</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="16">
+        <f>B30-B31</f>
+        <v>39406.249999999993</v>
+      </c>
+      <c r="C32" s="17">
+        <v>9.8876295304449471</v>
+      </c>
+      <c r="D32" s="16">
+        <f>C32*B32</f>
+        <v>389634.40118409612</v>
+      </c>
+      <c r="E32" s="22"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="17">
-        <f>A1*A12</f>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="21">
+        <f>SUM(D31:D32)</f>
+        <v>625695.82863319246</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="32">
+        <f>B24</f>
         <v>53300</v>
       </c>
-      <c r="C19" s="18">
-        <v>5.5467190048837516</v>
-      </c>
-      <c r="D19" s="17">
-        <f>C19*B19</f>
-        <v>295640.12296030397</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="17">
-        <f>A1*A13</f>
-        <v>44850.000000000007</v>
-      </c>
-      <c r="C20" s="18">
-        <v>9.8876295304449471</v>
-      </c>
-      <c r="D20" s="17">
-        <f>C20*B20</f>
-        <v>443460.18444045592</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="22">
-        <f>SUM(D19:D20)</f>
-        <v>739100.30740075989</v>
-      </c>
-      <c r="E21" s="3">
-        <f>B16-D21</f>
-        <v>821008.89259924006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+      <c r="C37" s="32">
+        <f>B31</f>
+        <v>42558.750000000007</v>
+      </c>
+      <c r="D37" s="26">
+        <f>C37-B37</f>
+        <v>-10741.249999999993</v>
+      </c>
+      <c r="E37" s="32">
+        <f>D37*C31</f>
+        <v>-59578.695511207559</v>
+      </c>
+      <c r="F37" s="27">
+        <f>C37/B37</f>
+        <v>0.79847560975609766</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="9">
+        <f>B25</f>
+        <v>44850</v>
+      </c>
+      <c r="C38" s="9">
+        <f>B32</f>
+        <v>39406.249999999993</v>
+      </c>
+      <c r="D38" s="3">
+        <f>C38-B38</f>
+        <v>-5443.7500000000073</v>
+      </c>
+      <c r="E38" s="9">
+        <f>D38*C32</f>
+        <v>-53825.783256359755</v>
+      </c>
+      <c r="F38" s="28">
+        <f>C38/B38</f>
+        <v>0.8786231884057969</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="11">
+        <f>SUM(E37:E38)</f>
+        <v>-113404.47876756731</v>
+      </c>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E40" s="5">
+        <f>E39/D26</f>
+        <v>-0.15343584305408278</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="17">
-        <f>A9*A7</f>
-        <v>71505.005000000005</v>
-      </c>
-      <c r="D25" s="24"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+      <c r="B41" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="32">
+        <f>B37</f>
+        <v>53300</v>
+      </c>
+      <c r="C42" s="32">
+        <f>B42*F42</f>
+        <v>47970</v>
+      </c>
+      <c r="D42" s="32">
+        <f>C42-B42</f>
+        <v>-5330</v>
+      </c>
+      <c r="E42" s="32">
+        <f>D42*C31</f>
+        <v>-29564.012296030396</v>
+      </c>
+      <c r="F42" s="33">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="17">
-        <f>A10*A7</f>
-        <v>36402.548000000003</v>
-      </c>
-      <c r="C26" s="18">
-        <v>5.5467190048837516</v>
-      </c>
-      <c r="D26" s="17">
-        <f>C26*B26</f>
-        <v>201914.70481779301</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+      <c r="B43" s="9">
+        <f>B38</f>
+        <v>44850</v>
+      </c>
+      <c r="C43" s="9">
+        <f>B43*F43</f>
+        <v>40365</v>
+      </c>
+      <c r="D43" s="9">
+        <f>C43-B43</f>
+        <v>-4485</v>
+      </c>
+      <c r="E43" s="9">
+        <f>D43*C32</f>
+        <v>-44346.018444045585</v>
+      </c>
+      <c r="F43" s="34">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="17">
-        <v>35102</v>
-      </c>
-      <c r="C27" s="18">
-        <v>9.8876295304449471</v>
-      </c>
-      <c r="D27" s="17">
-        <f>C27*B27</f>
-        <v>347075.57177767856</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="22">
-        <f>SUM(D26:D27)</f>
-        <v>548990.27659547154</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="33">
-        <f>B19</f>
-        <v>53300</v>
-      </c>
-      <c r="C32" s="33">
-        <f>B26</f>
-        <v>36402.548000000003</v>
-      </c>
-      <c r="D32" s="27">
-        <f>C32-B32</f>
-        <v>-16897.451999999997</v>
-      </c>
-      <c r="E32" s="33">
-        <f>D32*C26</f>
-        <v>-93725.418142510942</v>
-      </c>
-      <c r="F32" s="28">
-        <f>C32/B32</f>
-        <v>0.68297463414634152</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="10">
-        <f>B20</f>
-        <v>44850.000000000007</v>
-      </c>
-      <c r="C33" s="10">
-        <f>B27</f>
-        <v>35102</v>
-      </c>
-      <c r="D33" s="7">
-        <f>C33-B33</f>
-        <v>-9748.0000000000073</v>
-      </c>
-      <c r="E33" s="10">
-        <f>D33*C27</f>
-        <v>-96384.612662777421</v>
-      </c>
-      <c r="F33" s="29">
-        <f>C33/B33</f>
-        <v>0.78265328874024509</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="12">
-        <f>SUM(E32:E33)</f>
-        <v>-190110.03080528835</v>
-      </c>
-      <c r="F34" s="31"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E35" s="5">
-        <f>E34/B16</f>
-        <v>-0.12185687438115765</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="33">
-        <f>B32</f>
-        <v>53300</v>
-      </c>
-      <c r="C37" s="35">
-        <f>B37*F37</f>
-        <v>47970</v>
-      </c>
-      <c r="D37" s="33">
-        <f>C37-B37</f>
-        <v>-5330</v>
-      </c>
-      <c r="E37" s="33">
-        <f>D37*C26</f>
-        <v>-29564.012296030396</v>
-      </c>
-      <c r="F37" s="36">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="10">
-        <f>B33</f>
-        <v>44850.000000000007</v>
-      </c>
-      <c r="C38" s="37">
-        <f>B38*F38</f>
-        <v>40365.000000000007</v>
-      </c>
-      <c r="D38" s="10">
-        <f>C38-B38</f>
-        <v>-4485</v>
-      </c>
-      <c r="E38" s="10">
-        <f>D38*C27</f>
-        <v>-44346.018444045585</v>
-      </c>
-      <c r="F38" s="38">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="12">
-        <f>SUM(E37:E38)</f>
+      <c r="B44" s="10"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="11">
+        <f>SUM(E42:E43)</f>
         <v>-73910.030740075978</v>
       </c>
-      <c r="F39" s="31"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E40" s="23">
-        <f>E39/B16</f>
-        <v>-4.7374908589780752E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E41" s="3">
-        <f>E34-E39</f>
-        <v>-116200.00006521237</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E42" s="23">
-        <f>(E34-E39)/E34</f>
-        <v>0.61122498151728244</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E43" s="23">
-        <f>E39/E34</f>
-        <v>0.38877501848271756</v>
+      <c r="F44" s="30"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E45" s="22">
+        <f>E44/D26</f>
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E46" s="3">
+        <f>E39-E44</f>
+        <v>-39494.448027491337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E47" s="22">
+        <f>(E39-E44)/E39</f>
+        <v>0.34826180109199006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E48" s="22">
+        <f>E44/E39</f>
+        <v>0.65173819890800999</v>
       </c>
     </row>
   </sheetData>

--- a/datos/ejemplos_empresas.xlsx
+++ b/datos/ejemplos_empresas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanr\OneDrive\Documentos\GitHub\master-queseria\website\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11055F31-17DA-4C5B-9F6F-EDDA202C5C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{11055F31-17DA-4C5B-9F6F-EDDA202C5C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57A0C5DB-D395-491F-AA83-19FAE829065D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{36A48B76-50FA-4C2B-B697-2A79038C0BE9}"/>
   </bookViews>
@@ -106,9 +106,6 @@
     <t>Balance de materia</t>
   </si>
   <si>
-    <t>MP/ESP</t>
-  </si>
-  <si>
     <t>Balance total</t>
   </si>
   <si>
@@ -147,6 +144,9 @@
   </si>
   <si>
     <t>HFD</t>
+  </si>
+  <si>
+    <t>MP(ESM)</t>
   </si>
 </sst>
 </file>
@@ -593,10 +593,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Imagen 9">
+        <xdr:cNvPr id="8" name="Imagen 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4F07208-F4E6-CA31-F431-865EB0B467A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9897C3FA-9E6F-D92F-9A4E-5E9E3F36739F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -654,10 +654,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Imagen 10">
+        <xdr:cNvPr id="12" name="Imagen 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D55FDD15-DC39-1DD1-F81F-3BCEB613DB3E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3501BBE1-7232-A526-80E0-428D49238D2D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1179,13 +1179,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>0.25</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2">
@@ -1242,14 +1242,14 @@
         <v>0.25</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="2">
         <f>G9-G10</f>
         <v>0.25</v>
       </c>
       <c r="H11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1258,7 +1258,7 @@
         <v>0.65753424657534243</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
@@ -1266,25 +1266,25 @@
         <v>0.65753424657534243</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2">
         <f>(1-G9)/(1-G10)</f>
         <v>0.65753424657534243</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1341,7 +1341,7 @@
         <v>0.30310378273520855</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2">
@@ -1349,14 +1349,14 @@
         <v>0.28409090909090912</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G16" s="2">
         <f>G14-G15</f>
         <v>0.3012048192771084</v>
       </c>
       <c r="H16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1365,7 +1365,7 @@
         <v>0.54938716654650321</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2">
@@ -1373,25 +1373,25 @@
         <v>0.5901639344262295</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="2">
         <f>(1-G14)/(1-G15)</f>
         <v>0.5535714285714286</v>
       </c>
       <c r="H17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1419,19 +1419,19 @@
         <v>3.45</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>3.45</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20">
         <v>3.45</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1577,19 +1577,19 @@
         <v>20</v>
       </c>
       <c r="B36" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="D36" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="F36" s="31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1619,7 +1619,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B38" s="9">
         <f>B25</f>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="10"/>
@@ -1666,19 +1666,19 @@
         <v>20</v>
       </c>
       <c r="B41" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="D41" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="E41" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E41" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="F41" s="31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1707,7 +1707,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B43" s="9">
         <f>B38</f>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" s="10"/>
       <c r="C44" s="8"/>
